--- a/data/trans_orig/IQ17A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ17A-Habitat-trans_orig.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35803</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76244</t>
+          <t>76170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86055</t>
+          <t>85533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>16954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48074</t>
+          <t>47609</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>54403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>31206</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>39293</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>46447</t>
+          <t>46449</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>73417</t>
+          <t>72918</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>80661</t>
+          <t>80657</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5341,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5467,47 +5467,47 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>20384</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>27760</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>20384</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>14235</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>28200</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>112530</t>
+          <t>113352</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>123541</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>137939</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>150775</t>
+          <t>150836</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>255165</t>
+          <t>256012</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>271096</t>
+          <t>271506</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6543,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25139</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>48231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>58623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44140</t>
+          <t>43857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38977</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78116</t>
+          <t>78213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89968</t>
+          <t>90020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -8553,12 +8553,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -8664,12 +8664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -8775,47 +8775,47 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>30685</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>85,26%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>30422</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>30422</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34735</t>
+          <t>34437</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52291</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63609</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -9669,12 +9669,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40327</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>47454</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>39064</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>73909</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>85016</t>
+          <t>85459</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -10785,12 +10785,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>131835</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145161</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>129908</t>
+          <t>129320</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>146589</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>265711</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>287091</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -11911,12 +11911,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11981,12 +11981,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -12022,12 +12022,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21781</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12092,12 +12092,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12107,12 +12107,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -12916,12 +12916,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12931,12 +12931,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>48072</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>37941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45448</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13077,12 +13077,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13097,12 +13097,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81019</t>
+          <t>81883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91924</t>
+          <t>92254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13112,12 +13112,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -13921,12 +13921,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -14032,12 +14032,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14047,12 +14047,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14082,12 +14082,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14102,12 +14102,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>48895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>56656</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -14926,12 +14926,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -15037,12 +15037,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35630</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15052,12 +15052,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>36408</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15087,12 +15087,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>62429</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>70950</t>
+          <t>71152</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15122,12 +15122,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -15890,12 +15890,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -15931,12 +15931,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15946,12 +15946,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15966,12 +15966,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -15981,12 +15981,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16001,12 +16001,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36854</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16016,12 +16016,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -16042,12 +16042,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16057,12 +16057,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16077,12 +16077,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>124365</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>136089</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16112,12 +16112,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>246136</t>
+          <t>246342</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>263924</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -17203,12 +17203,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17218,12 +17218,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17238,12 +17238,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -17314,12 +17314,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -17349,12 +17349,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>31056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>37656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17364,12 +17364,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18208,12 +18208,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18223,12 +18223,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18243,12 +18243,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18258,12 +18258,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -18284,12 +18284,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18299,12 +18299,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18319,12 +18319,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>42644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18334,12 +18334,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>68998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76437</t>
+          <t>76539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18369,12 +18369,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -19178,12 +19178,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19193,12 +19193,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -19213,12 +19213,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>416</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19228,12 +19228,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -19248,12 +19248,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -19289,12 +19289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -19304,12 +19304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30796</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19359,12 +19359,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>44474</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54669</t>
+          <t>54499</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19374,12 +19374,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20147,7 +20147,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -20183,12 +20183,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20198,12 +20198,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20253,12 +20253,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -20294,12 +20294,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20309,12 +20309,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20344,12 +20344,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>54723</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -21112,12 +21112,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21127,12 +21127,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21147,12 +21147,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -21188,12 +21188,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21203,12 +21203,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21223,12 +21223,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21238,12 +21238,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21258,12 +21258,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21273,12 +21273,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -21299,12 +21299,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21314,12 +21314,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21334,12 +21334,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21349,12 +21349,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21369,12 +21369,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>202958</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21384,12 +21384,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
